--- a/FPSDemo/MiniTemplate/Datas/#player_skill_config.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#player_skill_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_skill_config" sheetId="1" r:id="Rd7e862085fc143af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_skill_config" sheetId="1" r:id="R329b8ec02cf14c12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -879,7 +879,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="4" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G6" s="5" t="b">
         <x:v>1</x:v>
@@ -900,25 +900,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="4" t="n">
-        <x:v>2.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N6" s="4" t="n">
-        <x:v>0.85</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="O6" s="4" t="n">
-        <x:v>80</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="P6" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R6" s="4" t="n">
-        <x:v>6.5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S6" s="4" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="T6" s="4" t="n">
         <x:v>0</x:v>

--- a/FPSDemo/MiniTemplate/Datas/#player_skill_config.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#player_skill_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_skill_config" sheetId="1" r:id="R329b8ec02cf14c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_skill_config" sheetId="1" r:id="Rf1a50cce6a5d45cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -953,7 +953,7 @@
       <x:c r="AD6" s="4"/>
       <x:c r="AE6" s="4"/>
       <x:c r="AF6" s="4" t="str">
-        <x:v>Skill_Push_Cast</x:v>
+        <x:v>Onomatopoeia_Roar Variant</x:v>
       </x:c>
       <x:c r="AG6" s="4" t="str">
         <x:v>Skill_Push_Hit</x:v>
@@ -1037,16 +1037,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="V7" s="4" t="n">
-        <x:v>4.5</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="W7" s="4" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="X7" s="4" t="n">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Y7" s="4" t="n">
-        <x:v>2.5</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="Z7" s="4" t="n">
         <x:v>5</x:v>
@@ -1060,17 +1060,17 @@
         <x:v>Grenade_1 |Throw</x:v>
       </x:c>
       <x:c r="AE7" s="4" t="str">
-        <x:v>Gernade</x:v>
+        <x:v>bomb</x:v>
       </x:c>
       <x:c r="AF7" s="4"/>
       <x:c r="AG7" s="4"/>
       <x:c r="AH7" s="4" t="str">
-        <x:v>Skill_Grenade_Explosion</x:v>
+        <x:v>Onomatopoeia_Pow Variant</x:v>
       </x:c>
       <x:c r="AI7" s="4"/>
       <x:c r="AJ7" s="4"/>
       <x:c r="AK7" s="4" t="str">
-        <x:v>Skill_Grenade_Explosion</x:v>
+        <x:v>Boom爆炸声</x:v>
       </x:c>
       <x:c r="AL7" s="4"/>
       <x:c r="AM7" s="4" t="str">

--- a/FPSDemo/MiniTemplate/Datas/#player_skill_config.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#player_skill_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_skill_config" sheetId="1" r:id="Rf1a50cce6a5d45cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_skill_config" sheetId="1" r:id="R58b19609dd5e4c1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1043,7 +1043,7 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="X7" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="Y7" s="4" t="n">
         <x:v>1.2</x:v>
